--- a/output/2023/sector_totals_v2.5_year2023.xlsx
+++ b/output/2023/sector_totals_v2.5_year2023.xlsx
@@ -492,22 +492,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1510.197572949912</v>
+        <v>1569.246838406009</v>
       </c>
       <c r="C3" t="n">
-        <v>102.7330427818503</v>
+        <v>94.69237213261202</v>
       </c>
       <c r="D3" t="n">
-        <v>603.3881849344436</v>
+        <v>622.6959146128409</v>
       </c>
       <c r="E3" t="n">
-        <v>1904.484113009062</v>
+        <v>1795.164322404381</v>
       </c>
       <c r="F3" t="n">
-        <v>161.2034860637608</v>
+        <v>156.7615849748126</v>
       </c>
       <c r="G3" t="n">
-        <v>76.72636373138552</v>
+        <v>71.06185604301008</v>
       </c>
     </row>
     <row r="4">
@@ -817,22 +817,22 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5845.001185340923</v>
+        <v>5904.05045079702</v>
       </c>
       <c r="C16" t="n">
-        <v>961.3553838144317</v>
+        <v>953.3147131651933</v>
       </c>
       <c r="D16" t="n">
-        <v>4169.725466537565</v>
+        <v>4189.033196215962</v>
       </c>
       <c r="E16" t="n">
-        <v>8330.275667245965</v>
+        <v>8220.955876641285</v>
       </c>
       <c r="F16" t="n">
-        <v>1652.07737341632</v>
+        <v>1647.635472327372</v>
       </c>
       <c r="G16" t="n">
-        <v>104.1711147369614</v>
+        <v>98.50660704858595</v>
       </c>
     </row>
   </sheetData>
